--- a/output/full_scan/batch_seq6_2026-10-05.xlsx
+++ b/output/full_scan/batch_seq6_2026-10-05.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6245</v>
+        <v>6209</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>987.403459100268</v>
+        <v>1192.699319220036</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.3529094079267</v>
+        <v>66.95759234502063</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28.64510337641178</v>
+        <v>29.95088900971809</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.8112233047320598</v>
+        <v>2.108198937056546</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4542472154485162</v>
+        <v>0.5903336528412417</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>951.3172721102852</v>
+        <v>1151.317272110285</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>238.5</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.38571763125495</v>
+        <v>64.38571757764632</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26.49859774900642</v>
+        <v>26.49859766537211</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.144878242876871</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.141207249232611</v>
+        <v>0.1412072500115053</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6190</v>
+        <v>6285</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>935.1422806876255</v>
+        <v>1141.091996979037</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>249.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>70.86758858782969</v>
+        <v>61.02580766137911</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16.90059135357352</v>
+        <v>16.66203141324435</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.114228068762558</v>
+        <v>2.679145182343033</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.7699768800893918</v>
+        <v>2.283272296016804</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6227</v>
+        <v>6278</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>934.1636648188104</v>
+        <v>1123.534298457574</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>142.5</v>
+        <v>220</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>67.8469896971561</v>
+        <v>67.06767829417417</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>38.87071317271514</v>
+        <v>26.49688129697775</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.716366481881053</v>
+        <v>2.130570492871875</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.9623619604427898</v>
+        <v>1.957874207786915</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6285</v>
+        <v>6187</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>931.0919969790384</v>
+        <v>1120.133194159222</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>249.5</v>
+        <v>1490</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.02580766594432</v>
+        <v>67.89342888202425</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>16.66203141006263</v>
+        <v>18.56991332311229</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.679145182343033</v>
+        <v>2.214595026890364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.283272295682975</v>
+        <v>16.25630647426184</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6187</v>
+        <v>6190</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>920.1331941592204</v>
+        <v>1105.142280687626</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1490</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>67.89342887462718</v>
+        <v>70.86758861986641</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>18.56991331611001</v>
+        <v>16.90059137983106</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.214595026890364</v>
+        <v>4.114228068762558</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>16.25630647504073</v>
+        <v>0.7699768799781201</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6209</v>
+        <v>6245</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>912.6993192200354</v>
+        <v>1102.403459100268</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>87.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>66.9575923199983</v>
+        <v>61.35290946670829</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>29.95088901957622</v>
+        <v>28.64510348491269</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.108198937056546</v>
+        <v>0.8112233047320598</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.5903336528523726</v>
+        <v>0.4542472152037098</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6278</v>
+        <v>6257</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>898.5342984575742</v>
+        <v>1097.581558133168</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>67.06767840620191</v>
+        <v>69.28851911165975</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>26.49688128002029</v>
+        <v>28.02663079414008</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.130570492871875</v>
+        <v>1.558155813316868</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.957874207453083</v>
+        <v>2.929625222080354</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6419</v>
+        <v>6196</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>858.9381103727404</v>
+        <v>1091.012589724893</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>171.5</v>
+        <v>679</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>66.94320109518924</v>
+        <v>78.79769824751671</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.24535388245911</v>
+        <v>27.7288403906775</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6.874543085381767</v>
+        <v>1.701258972489331</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.459349614346857</v>
+        <v>13.41000020437141</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6174</v>
+        <v>6419</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>853.3567867074144</v>
+        <v>1058.93811037274</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>60.5</v>
+        <v>171.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>80.01857453197536</v>
+        <v>66.94320109704225</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.43381954243716</v>
+        <v>15.24535394929089</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.816002588794585</v>
+        <v>6.874543085381767</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.663054217796242</v>
+        <v>1.459349614102036</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6292</v>
+        <v>6174</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>845.9289389624033</v>
+        <v>1053.356786707414</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>71.2</v>
+        <v>60.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>69.46382543358871</v>
+        <v>80.01857453323017</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>33.26006196027485</v>
+        <v>24.43381954243716</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.040522662170648</v>
+        <v>1.816002588794585</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2907113102595415</v>
+        <v>1.663054217796242</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6257</v>
+        <v>6227</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>842.5815581331686</v>
+        <v>1049.163664818811</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>260</v>
+        <v>142.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>69.28851910842633</v>
+        <v>67.84698953691736</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.02663076195226</v>
+        <v>38.87071323355819</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.558155813316868</v>
+        <v>1.716366481881053</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2.929625222102615</v>
+        <v>0.9623619598864188</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6204</v>
+        <v>6274</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>836.8742573419152</v>
+        <v>1018.225235544161</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>113</v>
+        <v>1780</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>66.78074407088786</v>
+        <v>72.829546386725</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>29.60696447350072</v>
+        <v>20.07923032172272</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.287425734191521</v>
+        <v>1.422523554416059</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.004686840689921</v>
+        <v>36.27696189548675</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6274</v>
+        <v>6213</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>818.2252355441606</v>
+        <v>1000.997920999815</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1780</v>
+        <v>751</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>72.82954637631821</v>
+        <v>81.2124613486185</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>20.07923029684659</v>
+        <v>29.27305117478663</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.422523554416059</v>
+        <v>1.111211844829839</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>36.2769618962657</v>
+        <v>16.9159471567701</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6197</v>
+        <v>6225</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>811.8642538838897</v>
+        <v>991.8602853536059</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>345</v>
+        <v>69.2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>69.08967270761582</v>
+        <v>62.42610311378375</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>18.46891446732048</v>
+        <v>24.82629401371509</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.786425388388962</v>
+        <v>0.7860285353605921</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.784701537189858</v>
+        <v>0.2023450005794322</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6168</v>
+        <v>6259</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>788.7451412315743</v>
+        <v>987.5533238330636</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>47.1</v>
+        <v>33.15</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>77.9514856850947</v>
+        <v>68.3998143457076</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>54.17514544509963</v>
+        <v>16.075767330539</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.133942483060304</v>
+        <v>2.143916498161071</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.8933187308226103</v>
+        <v>0.5685155115288975</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6259</v>
+        <v>6292</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>787.5533238330636</v>
+        <v>985.9289389624035</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>33.15</v>
+        <v>71.2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>68.39981433951178</v>
+        <v>69.46382550171563</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>16.075767330539</v>
+        <v>33.26006225428082</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.143916498161071</v>
+        <v>2.040522662170648</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.5685155115622781</v>
+        <v>0.2907113100592637</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6163</v>
+        <v>6415</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>786.565807324396</v>
+        <v>982.488310519632</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>43.4</v>
+        <v>442</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>60.04277919474107</v>
+        <v>55.55250780615243</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>12.59295004235738</v>
+        <v>9.983120435383354</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4.877913461164222</v>
+        <v>1.086912272687181</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.2489705013479509</v>
+        <v>3.122479258578182</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6196</v>
+        <v>6207</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>781.0125897248934</v>
+        <v>969.4991699192242</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>679</v>
+        <v>152</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>78.79769824338713</v>
+        <v>72.81583578916951</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>27.72884041973569</v>
+        <v>28.96668365022801</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.701258972489331</v>
+        <v>1.549916991922423</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>13.41000020259106</v>
+        <v>4.247043809068892</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6207</v>
+        <v>6204</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>769.4991699192242</v>
+        <v>951.8742573419152</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>72.81583577932052</v>
+        <v>66.7807440251807</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>28.96668363632517</v>
+        <v>29.60696442941541</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.549916991922423</v>
+        <v>2.287425734191521</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>4.24704380909114</v>
+        <v>1.004686840890208</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6226</v>
+        <v>6197</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>748.5422953985193</v>
+        <v>951.8642538838895</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>43</v>
+        <v>345</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>59.90782685295881</v>
+        <v>69.08967257293185</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>50.84121909264724</v>
+        <v>18.46891436333077</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.527642983277798</v>
+        <v>1.786425388388962</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.0406500011231898</v>
+        <v>3.784701540750561</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6290</v>
+        <v>6168</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>738.289332288128</v>
+        <v>908.7451412315744</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>281.5</v>
+        <v>47.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>60.74804288382654</v>
+        <v>77.95148571167562</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>29.96638809028087</v>
+        <v>54.17514568298277</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8600698258400924</v>
+        <v>2.133942483060304</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.1196139577026329</v>
+        <v>0.8933187307447135</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6210</v>
+        <v>6163</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>721.4982116504501</v>
+        <v>901.5658073244016</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>18</v>
+        <v>43.4</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>52.33331809482948</v>
+        <v>60.0427791754693</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3.772048232642145</v>
+        <v>12.59295002855384</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.117213775890669</v>
+        <v>4.877913461164222</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1594638048118686</v>
+        <v>0.2489705013256909</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6213</v>
+        <v>6191</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>695.9979209998152</v>
+        <v>894.6352995343607</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>751</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>81.21246134997368</v>
+        <v>59.0651497327348</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>29.27305122063532</v>
+        <v>14.82485844618803</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.111211844829839</v>
+        <v>2.216447131466333</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>16.91594715643627</v>
+        <v>0.4900357923293308</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6275</v>
+        <v>6239</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>692.3916560182824</v>
+        <v>840.4971084452565</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>47.65</v>
+        <v>297.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>62.17489043686546</v>
+        <v>57.71228212314681</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>34.6920358198845</v>
+        <v>14.24730357929734</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7678315146489382</v>
+        <v>1.794323743875838</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.234719346942793</v>
+        <v>2.155891444405164</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6415</v>
+        <v>6414</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>682.488310519632</v>
+        <v>821.5068926324537</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>442</v>
+        <v>407.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.55250778327415</v>
+        <v>59.91820224927241</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>9.983120264331204</v>
+        <v>20.61309506252672</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.086912272687181</v>
+        <v>1.040865957162955</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>3.122479259245781</v>
+        <v>5.410029408346483</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6225</v>
+        <v>6275</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>681.8602853536059</v>
+        <v>807.3916560182826</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>69.2</v>
+        <v>47.65</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>62.42610311057555</v>
+        <v>62.17489049196185</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>24.8262939366078</v>
+        <v>34.69203592042977</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7860285353605921</v>
+        <v>0.7678315146489382</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.2023450005794322</v>
+        <v>0.2347193468982862</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6205</v>
+        <v>6266</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>672.4657883540619</v>
+        <v>774</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>27</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>60.66347238860374</v>
+        <v>81.18496431399612</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>29.1565438988247</v>
+        <v>15.0964277954219</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.0465788354062</v>
+        <v>6.015981566461565</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.7967270385733791</v>
+        <v>0.2124344134052429</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6191</v>
+        <v>6438</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>669.6352995343384</v>
+        <v>772.4865967477559</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>85.90000000000001</v>
+        <v>167.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>59.06514923405097</v>
+        <v>70.96454852334551</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>14.82485841774026</v>
+        <v>29.37986660406269</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.216447131466333</v>
+        <v>1.945207743448961</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.4900357937758603</v>
+        <v>1.942846275020208</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6173</v>
+        <v>6164</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>668.9812167595936</v>
+        <v>761.3985962105155</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>292</v>
+        <v>13.85</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.13880837848586</v>
+        <v>75.38858562133655</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>39.23178822681808</v>
+        <v>25.61900106628429</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5878336145223004</v>
+        <v>4.79304447221803</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-3.782599433347297</v>
+        <v>0.1876662984476769</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6416</v>
+        <v>6282</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>655.8359216083963</v>
+        <v>753.9920926754446</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>119.5</v>
+        <v>44.45</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>62.49266294364093</v>
+        <v>53.22547247453052</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>32.74728654972524</v>
+        <v>16.25800730020209</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7854182136114892</v>
+        <v>1.905626046903036</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.2881096930207683</v>
+        <v>0.3482178680163289</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6426</v>
+        <v>6226</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>644.239452057384</v>
+        <v>748.5422953985193</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>357.5</v>
+        <v>43</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>60.11566749530814</v>
+        <v>59.90782685413959</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>40.92458088442226</v>
+        <v>50.84121908361534</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.8761314468801208</v>
+        <v>1.527642983277798</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-3.642404782296517</v>
+        <v>-0.0406500011165098</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6414</v>
+        <v>6442</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>641.5068926324537</v>
+        <v>746.0374509221072</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>407.5</v>
+        <v>1705</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>59.91820216352099</v>
+        <v>59.52100598171266</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20.61309507114107</v>
+        <v>14.22862175483041</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.040865957162955</v>
+        <v>1.825143108975478</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>5.410029409125384</v>
+        <v>3.81668754102367</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6282</v>
+        <v>6233</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>638.9920926754438</v>
+        <v>739.2521282961461</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>44.45</v>
+        <v>23.6</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.22547245859448</v>
+        <v>73.99736093692324</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16.25800728480632</v>
+        <v>28.2792647472927</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.905626046903036</v>
+        <v>1.487524098637373</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3482178681721074</v>
+        <v>0.3845289773212907</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6266</v>
+        <v>6290</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>634</v>
+        <v>738.2893322881279</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>27</v>
+        <v>281.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>81.18496431877084</v>
+        <v>60.74804289912687</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.09642782245826</v>
+        <v>29.96638808372009</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6.015981566461565</v>
+        <v>0.8600698258400924</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.2124344133718632</v>
+        <v>-0.1196139574800909</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6438</v>
+        <v>6210</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>632.4865967477548</v>
+        <v>721.4982116504501</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>167.5</v>
+        <v>18</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>70.96454862655565</v>
+        <v>52.33331808268337</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>29.37986645194164</v>
+        <v>3.772048171494044</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.945207743448961</v>
+        <v>2.117213775890669</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.942846272794787</v>
+        <v>0.159463804867504</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6239</v>
+        <v>6279</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>625.4971084452565</v>
+        <v>691.5136881584463</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>297.5</v>
+        <v>116.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>57.71228211580249</v>
+        <v>52.65024683985145</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14.24730357929734</v>
+        <v>31.97200505660047</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.794323743875838</v>
+        <v>1.110932964332558</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>2.155891444293872</v>
+        <v>0.8391746862911189</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6166</v>
+        <v>6214</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>584.0415500351365</v>
+        <v>685.5254323159573</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>129.5</v>
+        <v>188.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>57.93152860359159</v>
+        <v>61.00688965702381</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>26.52437867468845</v>
+        <v>31.24355462551044</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.624798298837234</v>
+        <v>0.2753204172920002</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.882962077838377</v>
+        <v>-1.473761876448352</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6291</v>
+        <v>6218</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>582.9808158076316</v>
+        <v>683.7828300200465</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>488</v>
+        <v>61.4</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>55.37975080987205</v>
+        <v>64.64748362470667</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>27.60541108724515</v>
+        <v>50.15325581731255</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4178382927218654</v>
+        <v>0.3877484026840178</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-3.309538962990789</v>
+        <v>0.1411155995553894</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6214</v>
+        <v>6423</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>580.5254323159573</v>
+        <v>681.1389357987408</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>188.5</v>
+        <v>92</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>61.00688973127534</v>
+        <v>63.93608456761629</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>31.24355460960885</v>
+        <v>25.75861454989954</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2753204172920002</v>
+        <v>1.913893579874082</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.473761876782166</v>
+        <v>0.9665254209544454</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6279</v>
+        <v>6456</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>576.5136881584463</v>
+        <v>674.9956194638172</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>116.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.65024692759661</v>
+        <v>69.99389694610309</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>31.97200500603108</v>
+        <v>32.01672308790071</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.110932964332558</v>
+        <v>1.499561946381718</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.8391746860685805</v>
+        <v>2.474178225063477</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6442</v>
+        <v>6202</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>576.0374509221077</v>
+        <v>674.5596368773201</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1705</v>
+        <v>60.8</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>59.52100597824425</v>
+        <v>57.73957142509699</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>14.22862178893783</v>
+        <v>16.3908151144836</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.825143108975478</v>
+        <v>2.806469994889999</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>3.816687537017714</v>
+        <v>0.6924951282836987</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6164</v>
+        <v>6205</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>571.3985962105155</v>
+        <v>672.4657883540619</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>13.85</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>75.38858561010225</v>
+        <v>60.66347243616357</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25.61900106080157</v>
+        <v>29.15654392585004</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4.79304447221803</v>
+        <v>1.0465788354062</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1876662984476769</v>
+        <v>0.796727038617874</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6202</v>
+        <v>6173</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>569.5596368773205</v>
+        <v>668.9812167595936</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>60.8</v>
+        <v>292</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>57.7395714516393</v>
+        <v>55.13880837469057</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>16.39081509643111</v>
+        <v>39.23178822435762</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.806469994889999</v>
+        <v>0.5878336145223004</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.6924951280945325</v>
+        <v>-3.782599433269404</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6233</v>
+        <v>6182</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>569.2521282961459</v>
+        <v>665.3600276644917</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>23.6</v>
+        <v>131.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>73.99736097478228</v>
+        <v>62.58191220043416</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>28.27926473818003</v>
+        <v>24.19886350994519</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.487524098637373</v>
+        <v>1.300079529195097</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.3845289772211486</v>
+        <v>2.437097768942131</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6423</v>
+        <v>6416</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>541.1389357987408</v>
+        <v>655.8359216083963</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>92</v>
+        <v>119.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>63.93608454625911</v>
+        <v>62.49266293877218</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.7586145417721</v>
+        <v>32.74728657525959</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.913893579874082</v>
+        <v>0.7854182136114892</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>1</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.9665254207763984</v>
+        <v>-0.2881096929985318</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6462</v>
+        <v>6435</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>530.0659419200634</v>
+        <v>654.1436503024096</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>103.5</v>
+        <v>276.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>56.14692218115437</v>
+        <v>65.60927686967116</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.1419248914474</v>
+        <v>15.3186078573632</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.085031656358036</v>
+        <v>5.262080186224658</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.8812818224293669</v>
+        <v>4.568790162381354</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6224</v>
+        <v>6189</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>527.4046463001574</v>
+        <v>651.3349732212134</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>79.7</v>
+        <v>49.4</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>48.27498888372186</v>
+        <v>56.94988016410657</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>34.43100895501625</v>
+        <v>21.95797042210144</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4064001330242358</v>
+        <v>1.132002124900701</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-1.43497763000629</v>
+        <v>0.2790613110134395</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6234</v>
+        <v>6462</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>520.2744628979873</v>
+        <v>645.065941920063</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>38.85</v>
+        <v>103.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>55.20399384513112</v>
+        <v>56.14692188675204</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>24.40516590395198</v>
+        <v>20.14192495666192</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8546943882370526</v>
+        <v>1.085031656358036</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.3333131724529812</v>
+        <v>0.8812818232082729</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>504.9956194638172</v>
+        <v>644.239452057384</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>357.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>69.99389696451928</v>
+        <v>60.11566748336995</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>32.01672306050983</v>
+        <v>40.92458089472936</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.499561946381718</v>
+        <v>0.8761314468801208</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2.474178224974453</v>
+        <v>-3.642404781584379</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6418</v>
+        <v>6175</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>500.7988726680511</v>
+        <v>639.713633642484</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>34.15</v>
+        <v>75.2</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>48.44347106021979</v>
+        <v>56.63200044700263</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>30.81845488006722</v>
+        <v>18.70636235061859</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.435381775603572</v>
+        <v>2.459623694707905</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.1575253109974653</v>
+        <v>1.122669079189633</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6175</v>
+        <v>6208</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>499.713633642484</v>
+        <v>589.1275417081741</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>75.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>56.63200047309842</v>
+        <v>57.59893748411898</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>18.70636240183801</v>
+        <v>16.02882796706414</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2.459623694707905</v>
+        <v>1.241715064706117</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.122669078933707</v>
+        <v>0.9492101007029372</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6194</v>
+        <v>6166</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>497.618720737537</v>
+        <v>584.0415500351365</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>30.05</v>
+        <v>129.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.99097665686501</v>
+        <v>57.93152862553261</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>21.2169487375063</v>
+        <v>26.52437869262312</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1967075430343796</v>
+        <v>0.624798298837234</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0262603997854796</v>
+        <v>1.882962077682601</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6182</v>
+        <v>6291</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>495.3600276644917</v>
+        <v>582.9808158076316</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>131.5</v>
+        <v>488</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>62.58191220293065</v>
+        <v>55.37975078808206</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>24.19886356508226</v>
+        <v>27.60541098622354</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.300079529195097</v>
+        <v>0.4178382927218654</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>2.437097768842003</v>
+        <v>-3.30953896121045</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6206</v>
+        <v>6217</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>492.3390498111498</v>
+        <v>577.2022486758137</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>137.5</v>
+        <v>178</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.09557669645427</v>
+        <v>54.28552473301227</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16.3255891036641</v>
+        <v>14.95896607375924</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6551061991660879</v>
+        <v>0.8514469295192205</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1868184853795969</v>
+        <v>0.8405894591977088</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6270</v>
+        <v>6263</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>490.8970750470888</v>
+        <v>555.2374226687905</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>30.25</v>
+        <v>167</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>55.44917807377665</v>
+        <v>60.12100010765887</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.36931932779187</v>
+        <v>18.63580591473813</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.669306749827112</v>
+        <v>1.211830462245563</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.2642769901518665</v>
+        <v>1.205389255640362</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6441</v>
+        <v>6451</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>489.9033871496025</v>
+        <v>530.668346029011</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>24.9</v>
+        <v>432</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>57.95887772370937</v>
+        <v>51.23546794106612</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.62258130450702</v>
+        <v>7.712937847368151</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7742326827886765</v>
+        <v>0.9909733449211195</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0039734643671802</v>
+        <v>1.080481614523284</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6443</v>
+        <v>6224</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>489.372212791597</v>
+        <v>527.4046463001574</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>28.2</v>
+        <v>79.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>57.97611019885377</v>
+        <v>48.27498878028624</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>28.25435083415683</v>
+        <v>34.43100894135896</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.037221279159695</v>
+        <v>0.4064001330242358</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.4406441343471842</v>
+        <v>-1.434977629928396</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6435</v>
+        <v>6234</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>484.1436503024096</v>
+        <v>520.2744628979876</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>276.5</v>
+        <v>38.85</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>65.60927684837199</v>
+        <v>55.20399384281502</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15.31860787860478</v>
+        <v>24.40516608088972</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>5.262080186224658</v>
+        <v>0.8546943882370526</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>4.568790162648439</v>
+        <v>0.3333131726421436</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6472</v>
+        <v>6432</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>468.9529078024893</v>
+        <v>516.6979613848683</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>420.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.46641691434682</v>
+        <v>59.17153382849776</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>27.11191620807455</v>
+        <v>23.36768151320269</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5472475343273633</v>
+        <v>1.223557074504443</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1893926913527264</v>
+        <v>1.679786408545714</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6189</v>
+        <v>6284</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>466.3349732212127</v>
+        <v>501.7251793497204</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>49.4</v>
+        <v>80.2</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>56.94988012040128</v>
+        <v>56.67377465742396</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>21.95797040716647</v>
+        <v>13.29071164381581</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.132002124900701</v>
+        <v>3.282925916180464</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.2790613110134395</v>
+        <v>0.6665518048113851</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6192</v>
+        <v>6418</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>464.662139266379</v>
+        <v>500.798872668051</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>110.5</v>
+        <v>34.15</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>42.51595863546261</v>
+        <v>48.44347709897142</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>30.88971121929737</v>
+        <v>30.81845652490174</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.379417980185734</v>
+        <v>2.435381775603572</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0502749922994276</v>
+        <v>-0.1575253163941301</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6217</v>
+        <v>6194</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>462.2022486758137</v>
+        <v>497.618720737535</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>178</v>
+        <v>30.05</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.28552470518434</v>
+        <v>49.99097632713515</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.95896606490645</v>
+        <v>21.21694889724008</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.8514469295192205</v>
+        <v>0.1967075430343796</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.8405894593535015</v>
+        <v>-0.0262603997187161</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6208</v>
+        <v>6206</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>449.1275417081739</v>
+        <v>492.3390498111497</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>137.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>57.59893742819347</v>
+        <v>48.09557667186618</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>16.02882800606978</v>
+        <v>16.325589122571</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.241715064706117</v>
+        <v>0.6551061991660879</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.9492101008364624</v>
+        <v>-0.186818485157056</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6417</v>
+        <v>6270</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>426.6398296540091</v>
+        <v>490.8970750470888</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>102.5</v>
+        <v>30.25</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>42.74434139306163</v>
+        <v>55.44917800040408</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>38.11080539893698</v>
+        <v>19.36931926379594</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.164742317735604</v>
+        <v>1.669306749827112</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.4254856457318814</v>
+        <v>0.2642769902408829</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6265</v>
+        <v>6441</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>420.5405824348117</v>
+        <v>489.9033871496025</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>49.05</v>
+        <v>24.9</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.07567608048391</v>
+        <v>57.95887792118505</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.49272949588084</v>
+        <v>20.622581299164</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.9907789043643696</v>
+        <v>0.7742326827886765</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.1671182008535434</v>
+        <v>0.0039734644561955</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6263</v>
+        <v>6443</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>415.2374226687904</v>
+        <v>489.372212791597</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>167</v>
+        <v>28.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>60.12100007995858</v>
+        <v>57.97611016600055</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>18.63580592802858</v>
+        <v>28.25435103367272</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.211830462245563</v>
+        <v>1.037221279159695</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>1.205389256085462</v>
+        <v>0.4406441343694384</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6451</v>
+        <v>6472</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>405.6683460290109</v>
+        <v>468.9529078024892</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>432</v>
+        <v>420.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.23546795919904</v>
+        <v>49.46641706917735</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7.712937843846813</v>
+        <v>27.11191645037785</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.9909733449211195</v>
+        <v>0.5472475343273633</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>1.080481613855661</v>
+        <v>0.1893926944683246</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6229</v>
+        <v>6192</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>387.7345727280068</v>
+        <v>464.662139266379</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>24.15</v>
+        <v>110.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>58.7876467044177</v>
+        <v>42.51595915587803</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.57555540089362</v>
+        <v>30.88971128382136</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.018611486489607</v>
+        <v>1.379417980185734</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0969026814815019</v>
+        <v>0.050274992633243</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6235</v>
+        <v>6464</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>375.3956412708301</v>
+        <v>433.5924553177015</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>38.35</v>
+        <v>77.2</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.77009266845288</v>
+        <v>49.21960365558989</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.35900931597129</v>
+        <v>23.36243838001337</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.969053224882824</v>
+        <v>0.3602887766181439</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0688682449509497</v>
+        <v>-0.0282668734822786</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6284</v>
+        <v>6417</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>361.7251793497204</v>
+        <v>426.6398296540091</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>80.2</v>
+        <v>102.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>56.67377464470086</v>
+        <v>42.74434150876236</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.29071164050869</v>
+        <v>38.11080546152381</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>3.282925916180464</v>
+        <v>1.164742317735604</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.6665518047446259</v>
+        <v>0.4254856453535702</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6409</v>
+        <v>6265</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>359.5276944380798</v>
+        <v>420.5405824348117</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>891</v>
+        <v>49.05</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>42.86387738260053</v>
+        <v>44.07567608611109</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.49838454575593</v>
+        <v>18.49272937285797</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6377668447766361</v>
+        <v>0.9907789043643696</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>3.480571403158514</v>
+        <v>0.1671182010538277</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6223</v>
+        <v>6446</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>353.8644938623164</v>
+        <v>419.2015016593261</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>5520</v>
+        <v>1190</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.29565969374249</v>
+        <v>43.81037456660452</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13.28499311304095</v>
+        <v>18.13462451307083</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.8875947488879278</v>
+        <v>0.4715652383218525</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-5.190254681636304</v>
+        <v>-0.8703919830279432</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6277</v>
+        <v>6229</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>353.7561327949977</v>
+        <v>387.7345727280068</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>24.15</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45.45215752741197</v>
+        <v>58.78764659143014</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>12.99543658889716</v>
+        <v>17.57555539534855</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7973291690883643</v>
+        <v>1.018611486489607</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0433273616030218</v>
+        <v>0.096902681514882</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6165</v>
+        <v>6235</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>348.5022538571724</v>
+        <v>375.3956412708293</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>48.6</v>
+        <v>38.35</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.32923113170988</v>
+        <v>46.7700918774656</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>17.30624410190756</v>
+        <v>17.35900971775875</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5620833581825124</v>
+        <v>1.969053224882824</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0553356531486999</v>
+        <v>0.0688682457966102</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6244</v>
+        <v>6409</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>346.7365588780019</v>
+        <v>364.6396682195479</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>23.25</v>
+        <v>891</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.28226274814072</v>
+        <v>42.86387736675748</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>19.65533424320946</v>
+        <v>15.49838449381402</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.275586812228736</v>
+        <v>1.014438448406498</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1553648136978226</v>
+        <v>3.480571400933037</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6432</v>
+        <v>6223</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>346.6979613848683</v>
+        <v>353.8644938623171</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>5520</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>59.17153382962229</v>
+        <v>51.29565971112872</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>23.36768151320269</v>
+        <v>13.28499316959548</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.223557074504443</v>
+        <v>0.8875947488879278</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>1.679786408523454</v>
+        <v>-5.190254680524134</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6446</v>
+        <v>6277</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>344.2015016593261</v>
+        <v>353.7561327949977</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>1190</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>43.81037458555754</v>
+        <v>45.45215754836463</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.13462447400013</v>
+        <v>12.99543662325262</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4715652383218525</v>
+        <v>0.7973291690883643</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.8703919841407313</v>
+        <v>-0.0433273616475198</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6412</v>
+        <v>6449</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>339.9943182820367</v>
+        <v>353.3415638686151</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>227</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45.03183311342291</v>
+        <v>53.01743587921934</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21.33969588952394</v>
+        <v>12.5724973804067</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.359046421414263</v>
+        <v>1.272632677577796</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.3229383403706269</v>
+        <v>2.481133713129815</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6411</v>
+        <v>6165</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>339.6459778646416</v>
+        <v>348.5022538571724</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>78.7</v>
+        <v>48.6</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>49.94992627923738</v>
+        <v>48.32923078044203</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>8.145365810727538</v>
+        <v>17.3062442290467</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.565259627855545</v>
+        <v>0.5620833581825124</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.1927910797247773</v>
+        <v>0.0553356537273135</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6198</v>
+        <v>6201</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>337.7139006314946</v>
+        <v>347.8052381116787</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>19.45</v>
+        <v>44.05</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>52.34880239264893</v>
+        <v>41.53184338153</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>8.165140317128287</v>
+        <v>27.80881453397095</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.969875959834613</v>
+        <v>1.893836850356896</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.8992632082247367</v>
+        <v>-0.0105635499148673</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6220</v>
+        <v>6244</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>336.8582043684955</v>
+        <v>346.7365588780019</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>25.3</v>
+        <v>23.25</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>42.78646845439226</v>
+        <v>47.2822627223159</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9.40823769958711</v>
+        <v>19.65533436568374</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.603719673546915</v>
+        <v>1.275586812228736</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.08867093140379489</v>
+        <v>0.1553648136978226</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6236</v>
+        <v>6412</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>336.6871593835509</v>
+        <v>339.9943182820364</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.74956789232173</v>
+        <v>45.0318332315351</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>14.31714175550805</v>
+        <v>21.33969588031897</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0</v>
+        <v>1.359046421414263</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.1504323279953228</v>
+        <v>0.3229383401480958</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6474</v>
+        <v>6411</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>336.1852707835842</v>
+        <v>339.6459778646416</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>35.65</v>
+        <v>78.7</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>43.00693054425788</v>
+        <v>49.94992628595622</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.59065136596956</v>
+        <v>8.145365755613808</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.261198853859703</v>
+        <v>1.565259627855545</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.1019482970674345</v>
+        <v>0.1927910798583098</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6269</v>
+        <v>6198</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>329.4388222145621</v>
+        <v>337.7139006314946</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>19.45</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>49.09851102121819</v>
+        <v>52.34880239979148</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.02179682350544</v>
+        <v>8.165140328371074</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.7610146016552998</v>
+        <v>1.969875959834613</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0713545077984295</v>
+        <v>0.8992632080021927</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6201</v>
+        <v>6220</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>327.8052381116786</v>
+        <v>336.8582043684956</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>44.05</v>
+        <v>25.3</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>41.53184336894729</v>
+        <v>42.78646866846335</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>27.80881455006651</v>
+        <v>9.40823823799148</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.893836850356896</v>
+        <v>1.603719673546915</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0105635498703634</v>
+        <v>0.08867093128139431</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6464</v>
+        <v>6236</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>323.5924553177015</v>
+        <v>336.6871593835509</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>77.2</v>
+        <v>0</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.21960387997335</v>
+        <v>40.74956835632278</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>23.36243825172518</v>
+        <v>14.31714175498696</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3602887766181439</v>
+        <v>0</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0282668735045269</v>
+        <v>-0.1504323279953228</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6405</v>
+        <v>6474</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>317.5331932530871</v>
+        <v>336.1852707835842</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>41.9</v>
+        <v>35.65</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>50.42018229132243</v>
+        <v>43.00693076786703</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>23.18963862481973</v>
+        <v>13.59065146766653</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.153319325308715</v>
+        <v>1.261198853859703</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.4117460566545207</v>
+        <v>0.1019482967781265</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6167</v>
+        <v>6269</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>317.3728058860033</v>
+        <v>329.4388222145621</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>10.25</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.43303035037788</v>
+        <v>49.09851099304769</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.36887869948825</v>
+        <v>13.02179680989611</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.536005280676673</v>
+        <v>0.7610146016552998</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0216313962450851</v>
+        <v>-0.07135450775392491</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6228</v>
+        <v>6405</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>315.7874731334221</v>
+        <v>317.5331932530871</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>18</v>
+        <v>41.9</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>55.3685261942702</v>
+        <v>50.42018228791372</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.92390182587365</v>
+        <v>23.18963860625366</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.211316884840442</v>
+        <v>2.153319325308715</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>1.518757386210488</v>
+        <v>0.4117460566545207</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6170</v>
+        <v>6167</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>299.5664404967076</v>
+        <v>317.3728058860036</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>48.65</v>
+        <v>10.25</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>54.40328243404172</v>
+        <v>46.43303053132141</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>18.75122117872316</v>
+        <v>13.36887902295255</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.031056801999892</v>
+        <v>1.536005280676673</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.077243448347858</v>
+        <v>0.0216313963213652</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6243</v>
+        <v>6215</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>298.0755170270304</v>
+        <v>316.6185936616299</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>40.2</v>
+        <v>97.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>51.39670143326349</v>
+        <v>49.49181834807032</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17.30339607209124</v>
+        <v>9.53873244022264</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.8853685309664928</v>
+        <v>1.350549279482732</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.5410742265053935</v>
+        <v>0.09701203617732609</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6215</v>
+        <v>6228</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>296.6185936616299</v>
+        <v>315.7874731334222</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>97.8</v>
+        <v>18</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.4918177372062</v>
+        <v>55.36852616976353</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>9.538732424434214</v>
+        <v>14.92390201195708</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.350549279482732</v>
+        <v>1.211316884840442</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0970120355096844</v>
+        <v>1.518757386266124</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6216</v>
+        <v>6170</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>284.4746103698494</v>
+        <v>299.5664404967076</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>19.9</v>
+        <v>48.65</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.99426119434702</v>
+        <v>54.40328233111763</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>35.08946602098173</v>
+        <v>18.7512212561619</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8713597045321447</v>
+        <v>1.031056801999892</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1142256888393289</v>
+        <v>0.0772434483033491</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6470</v>
+        <v>6243</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>273.7400331836079</v>
+        <v>298.0755170270304</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>42.6</v>
+        <v>40.2</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45.96342171107015</v>
+        <v>51.39670140556329</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>21.11394888101874</v>
+        <v>17.30339601905242</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.084063288981255</v>
+        <v>0.8853685309664928</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,11 +5552,11 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0104080110310039</v>
+        <v>0.5410742266166526</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>270.7221173586494</v>
+        <v>290.7221173586494</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>92.3</v>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>52.16028878847189</v>
+        <v>52.16028889431889</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.85620782470382</v>
+        <v>14.85620787513213</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.5058141464854492</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1954074267827135</v>
+        <v>-0.1954074271641233</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6261</v>
+        <v>6216</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>264.6291446001803</v>
+        <v>284.4746103698494</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>48.36284294526146</v>
+        <v>44.99426122246518</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>11.38885884630811</v>
+        <v>35.08946602339656</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.921489650966291</v>
+        <v>0.8713597045321447</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.2581082005124709</v>
+        <v>0.1142256888059489</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6246</v>
+        <v>6470</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>263.4321696074692</v>
+        <v>273.7400331836079</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>12.7</v>
+        <v>42.6</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.79194465472363</v>
+        <v>45.96342159990383</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>23.6646513795234</v>
+        <v>21.11394891413972</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.0658850314256028</v>
+        <v>1.084063288981255</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0052353404852229</v>
+        <v>0.0104080110643806</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6230</v>
+        <v>6261</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>261.6636199174424</v>
+        <v>264.6291446001803</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>113</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>53.54251211202848</v>
+        <v>48.36284294526146</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.37578885407999</v>
+        <v>11.38885887196423</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4177299570376853</v>
+        <v>0.921489650966291</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.2391898093780483</v>
+        <v>0.2581082005347191</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6177</v>
+        <v>6246</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>259.1338085003661</v>
+        <v>263.4321696074695</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>45.3</v>
+        <v>12.7</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>37.00390282523089</v>
+        <v>47.79194459726327</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15.07278364818439</v>
+        <v>23.66465138435812</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.191401605128115</v>
+        <v>0.0658850314256028</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1800959287970918</v>
+        <v>-0.0052353404518424</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6281</v>
+        <v>6230</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>258.9746660253159</v>
+        <v>261.6636199174425</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>50.7</v>
+        <v>113</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>38.46277154736017</v>
+        <v>53.54251246893426</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>10.42003879903056</v>
+        <v>15.3757888476734</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.237112831705408</v>
+        <v>0.4177299570376853</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0201182500080254</v>
+        <v>0.2391898092667833</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6188</v>
+        <v>6177</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>253.084856998494</v>
+        <v>259.1338085003662</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>61.6</v>
+        <v>45.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>34.43722171926416</v>
+        <v>37.00390283925471</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>28.61289712545994</v>
+        <v>15.07278364704289</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.638931619631928</v>
+        <v>1.191401605128115</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.2280233490579155</v>
+        <v>-0.1800959287970918</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6237</v>
+        <v>6281</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>246.7825421154957</v>
+        <v>258.9746660253159</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>35.6</v>
+        <v>50.7</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>52.30717271670368</v>
+        <v>38.4627715754597</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>24.11071989635165</v>
+        <v>10.42003875345972</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.8085636500743097</v>
+        <v>1.237112831705408</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.234161595033065</v>
+        <v>-0.0201182500302773</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6185</v>
+        <v>6188</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>239.543988922877</v>
+        <v>253.0848569984942</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>12.45</v>
+        <v>61.6</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>41.71569444623298</v>
+        <v>34.43722039520036</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>20.92516934334158</v>
+        <v>28.61289769648955</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.8745027454674149</v>
+        <v>1.638931619631928</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0324849546482488</v>
+        <v>0.2280233510830487</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6465</v>
+        <v>6237</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>222.0855606221243</v>
+        <v>246.7825421154956</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>40.85</v>
+        <v>35.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>33.67539417662509</v>
+        <v>52.30717277142511</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>10.80886668098884</v>
+        <v>24.11071991872876</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.670087328469416</v>
+        <v>0.8085636500743097</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1393505674675064</v>
+        <v>0.2341615950553181</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6161</v>
+        <v>6185</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>219.0573750898986</v>
+        <v>239.543988922877</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>49.15</v>
+        <v>12.45</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.11113403889289</v>
+        <v>41.71569461452167</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>10.1071018478844</v>
+        <v>20.92516925362225</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.6055679113446032</v>
+        <v>0.8745027454674149</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.150801147263232</v>
+        <v>0.0324849545926131</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6184</v>
+        <v>6465</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>217.2123935180579</v>
+        <v>222.0855606221243</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>40.1</v>
+        <v>40.85</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.5161913750532</v>
+        <v>33.67539425952307</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>29.84463108843017</v>
+        <v>10.80886668098884</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4949224916451444</v>
+        <v>1.670087328469416</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0928656047041781</v>
+        <v>0.1393505673530868</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6449</v>
+        <v>6161</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>213.3415638686152</v>
+        <v>219.0573750898986</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>227</v>
+        <v>49.15</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>53.01743593269406</v>
+        <v>47.11113408528828</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.57249735467893</v>
+        <v>10.1071018491153</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.272632677577796</v>
+        <v>0.6055679113446032</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>2.481133711683265</v>
+        <v>0.1508011472854916</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6203</v>
+        <v>6184</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>175.3924658534948</v>
+        <v>217.2123935180577</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>60</v>
+        <v>40.1</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46.96401691422688</v>
+        <v>42.5161913750532</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>8.643042224809134</v>
+        <v>29.84463108843017</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7607960280301664</v>
+        <v>0.4949224916451444</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1537352791495988</v>
+        <v>0.0928656047041781</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6272</v>
+        <v>6222</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>160.7510985081666</v>
+        <v>208.4034824236446</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>25.25</v>
+        <v>19.9</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>43.7993207659461</v>
+        <v>52.15882997953359</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>23.40165390513425</v>
+        <v>8.012229357877084</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.320213802207071</v>
+        <v>0.5343212339258362</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.2292596956853848</v>
+        <v>-0.2505086856198134</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6183</v>
+        <v>6203</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>145.4698866783327</v>
+        <v>175.3924658534943</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>60</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>47.89831066480449</v>
+        <v>46.96401747976402</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>10.22672120628042</v>
+        <v>8.643042155634765</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.8487913790353815</v>
+        <v>0.7607960280301664</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.06437693313009769</v>
+        <v>0.1537352783261915</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6276</v>
+        <v>6272</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>120.769023472627</v>
+        <v>160.7510985081668</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>19.75</v>
+        <v>25.25</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>51.56473810849791</v>
+        <v>43.7993211652289</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.83443034614607</v>
+        <v>23.40165387976354</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.9510386984641216</v>
+        <v>0.320213802207071</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.699099650534462</v>
+        <v>-0.2292596957521461</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6283</v>
+        <v>6183</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>87.06754741820207</v>
+        <v>145.4698866783327</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>18.9</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>43.72170428401537</v>
+        <v>47.89831074907257</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19.34720548751779</v>
+        <v>10.22672124405805</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7509716446711939</v>
+        <v>0.8487913790353815</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1076230112163729</v>
+        <v>0.06437693299656649</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6222</v>
+        <v>6276</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>68.40348242364448</v>
+        <v>120.769023472627</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>19.9</v>
+        <v>19.75</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>52.15882998388714</v>
+        <v>51.56473808031692</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.012229376971156</v>
+        <v>19.83443034760185</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5343212339258362</v>
+        <v>0.9510386984641216</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,11 +6559,64 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2505086856531929</v>
+        <v>-0.6990996503564307</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6283</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>淳安</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>87.06754741820204</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>43.72170433916536</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>19.34720590064587</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.7509716446711939</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.1076230117282195</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
